--- a/gst_calculator.xlsx
+++ b/gst_calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F52785-744E-42E4-A04A-70AB2F4877F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CF2D28-8DA0-4317-9990-F931257B502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13140" yWindow="0" windowWidth="26796" windowHeight="16656" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4392" yWindow="0" windowWidth="24408" windowHeight="16656" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio Summary" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>Overall Portfolio Summary</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Delisted Tickers</t>
+  </si>
+  <si>
+    <t>ME1</t>
   </si>
   <si>
     <t>Stock Code</t>
@@ -178,7 +181,7 @@
     <t>Net ST Gain/(Loss)</t>
   </si>
   <si>
-    <t>Gain/Loss (before discount)</t>
+    <t>NET Gain/Loss (before discount)</t>
   </si>
   <si>
     <t>PREV LOSS (MANUAL)</t>
@@ -230,7 +233,7 @@
     <numFmt numFmtId="169" formatCode="d/m/yyyy\ hh:mm"/>
     <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -327,6 +330,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF3F3F3"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -366,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -407,35 +416,54 @@
     </xf>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -979,7 +1007,9 @@
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6">
+        <v>6</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1037,7 +1067,9 @@
       <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1092,43 +1124,43 @@
     </row>
     <row r="12" spans="1:26" ht="54" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
@@ -28846,37 +28878,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -37336,7 +37368,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="9.21875" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
@@ -37345,155 +37377,155 @@
     <col min="8" max="8" width="8.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" customWidth="1"/>
     <col min="10" max="10" width="12.21875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" customWidth="1"/>
     <col min="12" max="12" width="11.88671875" customWidth="1"/>
     <col min="13" max="13" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.8">
       <c r="B1" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-    </row>
-    <row r="2" spans="1:26" ht="16.8">
-      <c r="B2" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="26">
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+    </row>
+    <row r="2" spans="1:26" ht="16.8">
+      <c r="B2" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="25">
         <f>IF(C1&lt;&gt;"", DATE(VALUE(LEFT(C1,4)), 7, 1), "")</f>
         <v>45474</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-    </row>
-    <row r="3" spans="1:26" ht="16.8">
-      <c r="B3" s="25" t="s">
+      <c r="E2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="26">
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+    </row>
+    <row r="3" spans="1:26" ht="16.8">
+      <c r="B3" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="25">
         <f>IF(C1&lt;&gt;"", DATE(VALUE(RIGHT(C1,4)), 6, 30), "")</f>
         <v>45838</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
     </row>
     <row r="4" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
     </row>
     <row r="5" spans="1:26" ht="16.8">
-      <c r="B5" s="25" t="s">
-        <v>38</v>
+      <c r="B5" s="24" t="s">
+        <v>39</v>
       </c>
       <c r="C5" s="27">
         <f>SUMIFS(J18:J1013, I18:I1013, "Yes", J18:J1013, "&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="24"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="28"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
     </row>
     <row r="6" spans="1:26" ht="21.75" customHeight="1">
       <c r="A6" s="29"/>
-      <c r="B6" s="25" t="s">
-        <v>39</v>
+      <c r="B6" s="24" t="s">
+        <v>40</v>
       </c>
       <c r="C6" s="27">
         <f>SUMIFS(J18:J1013, I18:I1013, "Yes", J18:J1013, "&lt;0")</f>
@@ -37524,8 +37556,8 @@
     </row>
     <row r="7" spans="1:26" ht="21.75" customHeight="1">
       <c r="A7" s="29"/>
-      <c r="B7" s="25" t="s">
-        <v>40</v>
+      <c r="B7" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="C7" s="27">
         <f>SUMIFS(J18:J1013, I18:I1013, "No", J18:J1013, "&gt;0")</f>
@@ -37556,8 +37588,8 @@
     </row>
     <row r="8" spans="1:26" ht="21.75" customHeight="1">
       <c r="A8" s="29"/>
-      <c r="B8" s="25" t="s">
-        <v>41</v>
+      <c r="B8" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="C8" s="27">
         <f>SUMIFS(J18:J1013, I18:I1013, "No", J18:J1013, "&lt;0")</f>
@@ -37590,7 +37622,7 @@
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
       <c r="A9" s="29"/>
       <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
@@ -37617,8 +37649,8 @@
     </row>
     <row r="10" spans="1:26" ht="21.75" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="25" t="s">
-        <v>42</v>
+      <c r="B10" s="24" t="s">
+        <v>43</v>
       </c>
       <c r="C10" s="27">
         <f>C5+C6</f>
@@ -37650,8 +37682,8 @@
     </row>
     <row r="11" spans="1:26" ht="21.75" customHeight="1">
       <c r="A11" s="29"/>
-      <c r="B11" s="25" t="s">
-        <v>43</v>
+      <c r="B11" s="24" t="s">
+        <v>44</v>
       </c>
       <c r="C11" s="27">
         <f>C7+C8</f>
@@ -37683,10 +37715,10 @@
     </row>
     <row r="12" spans="1:26" ht="21.75" customHeight="1">
       <c r="A12" s="29"/>
-      <c r="B12" s="31" t="s">
-        <v>44</v>
+      <c r="B12" s="32" t="s">
+        <v>45</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>IFERROR(C10+C11, 0)</f>
         <v>0</v>
       </c>
@@ -37716,7 +37748,7 @@
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
       <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
+      <c r="B13" s="34"/>
       <c r="C13" s="29"/>
       <c r="D13" s="29"/>
       <c r="E13" s="29"/>
@@ -37742,44 +37774,44 @@
       <c r="Y13" s="29"/>
       <c r="Z13" s="29"/>
     </row>
-    <row r="14" spans="1:26" ht="21.75" customHeight="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34" t="s">
-        <v>45</v>
+    <row r="14" spans="1:26" ht="24" customHeight="1">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36" t="s">
+        <v>46</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <v>0</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-    </row>
-    <row r="15" spans="1:26" ht="21.75" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37" t="s">
-        <v>46</v>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+    </row>
+    <row r="15" spans="1:26" ht="24" customHeight="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39" t="s">
+        <v>47</v>
       </c>
-      <c r="C15" s="38" t="e">
+      <c r="C15" s="40" t="e">
         <f ca="1">_xludf.LET(
     CurrentNetLT, C10,
     CurrentNetST, C11,
@@ -37791,102 +37823,113 @@
     NetLT_AfterLoss, CurrentNetLT - LossAppliedToLT,
     EligibleLT_ForDiscount, MAX(0, NetLT_AfterLoss),
     DiscountAmount, EligibleLT_ForDiscount * 0.5,
-    FinalNetGainOrLoss, (NetLT_AfterLoss - DiscountAmount) + NetST_AfterLoss,
-    FinalNetGainOrLoss
+    AssessableComponent, (NetLT_AfterLoss - DiscountAmount) + NetST_AfterLoss,
+    IF(AssessableComponent &gt;= 0,
+        AssessableComponent,
+        _xludf.LET(
+           CurrentYearNetLossComponent, IF(CurrentNetLT + CurrentNetST &lt; 0, -(CurrentNetLT + CurrentNetST), 0),
+           UnusedPriorLossComponent, LossFromB4 - LossAppliedToST - LossAppliedToLT,
+           TotalLossToCarryForward, CurrentYearNetLossComponent + UnusedPriorLossComponent,
+           -TotalLossToCarryForward
+        )
+    )
 )</f>
         <v>#NAME?</v>
       </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="36"/>
-      <c r="Z15" s="36"/>
-    </row>
-    <row r="16" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
+      <c r="D15" s="41" t="e">
+        <f ca="1">IF(C15&lt;0,"LOSS CARRIED FORWARD", "GAIN")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+    </row>
+    <row r="16" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A16" s="38"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
     </row>
     <row r="17" spans="1:26" ht="57.75" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
@@ -37905,30 +37948,17 @@
     <row r="18" spans="1:26" ht="16.5" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="39"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="3"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="39"/>
+      <c r="G18" s="44"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29"/>
+      <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1">
       <c r="A19" s="3"/>
@@ -38017,12 +38047,12 @@
     <row r="25" spans="1:26" ht="16.5" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="39"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="40"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="45"/>
       <c r="I25" s="3"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
@@ -38031,12 +38061,10 @@
     <row r="26" spans="1:26" ht="16.5" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="44"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45"/>
       <c r="I26" s="3"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
@@ -38045,12 +38073,11 @@
     <row r="27" spans="1:26" ht="16.5" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="44"/>
       <c r="E27" s="10"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="3"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
@@ -38059,12 +38086,10 @@
     <row r="28" spans="1:26" ht="16.5" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="44"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="40"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="3"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
@@ -38073,12 +38098,10 @@
     <row r="29" spans="1:26" ht="16.5" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="44"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="45"/>
       <c r="I29" s="3"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
@@ -38087,12 +38110,10 @@
     <row r="30" spans="1:26" ht="16.5" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="44"/>
       <c r="E30" s="10"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="45"/>
       <c r="I30" s="3"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
@@ -38101,12 +38122,10 @@
     <row r="31" spans="1:26" ht="16.5" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="44"/>
       <c r="E31" s="10"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="45"/>
       <c r="I31" s="3"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
@@ -38114,84 +38133,84 @@
     </row>
     <row r="32" spans="1:26" ht="16.5" customHeight="1">
       <c r="E32" s="10"/>
-      <c r="H32" s="40"/>
+      <c r="H32" s="45"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
     </row>
     <row r="33" spans="5:12" ht="16.5" customHeight="1">
       <c r="E33" s="10"/>
-      <c r="H33" s="40"/>
+      <c r="H33" s="45"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
     </row>
     <row r="34" spans="5:12" ht="16.5" customHeight="1">
       <c r="E34" s="10"/>
-      <c r="H34" s="40"/>
+      <c r="H34" s="45"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="5:12" ht="16.5" customHeight="1">
       <c r="E35" s="10"/>
-      <c r="H35" s="40"/>
+      <c r="H35" s="45"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
     </row>
     <row r="36" spans="5:12" ht="16.5" customHeight="1">
       <c r="E36" s="10"/>
-      <c r="H36" s="40"/>
+      <c r="H36" s="45"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
     </row>
     <row r="37" spans="5:12" ht="16.5" customHeight="1">
       <c r="E37" s="10"/>
-      <c r="H37" s="40"/>
+      <c r="H37" s="45"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
     </row>
     <row r="38" spans="5:12" ht="16.5" customHeight="1">
       <c r="E38" s="10"/>
-      <c r="H38" s="40"/>
+      <c r="H38" s="45"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
     </row>
     <row r="39" spans="5:12" ht="16.5" customHeight="1">
       <c r="E39" s="10"/>
-      <c r="H39" s="40"/>
+      <c r="H39" s="45"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
     </row>
     <row r="40" spans="5:12" ht="16.5" customHeight="1">
       <c r="E40" s="10"/>
-      <c r="H40" s="40"/>
+      <c r="H40" s="45"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
     </row>
     <row r="41" spans="5:12" ht="16.5" customHeight="1">
       <c r="E41" s="10"/>
-      <c r="H41" s="40"/>
+      <c r="H41" s="45"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
     </row>
     <row r="42" spans="5:12" ht="16.5" customHeight="1">
       <c r="E42" s="10"/>
-      <c r="H42" s="40"/>
+      <c r="H42" s="45"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="5:12" ht="16.5" customHeight="1">
       <c r="E43" s="10"/>
-      <c r="H43" s="40"/>
+      <c r="H43" s="45"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
